--- a/mod_project/data_tables/qol_class_text.xlsx
+++ b/mod_project/data_tables/qol_class_text.xlsx
@@ -612,14 +612,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>They have no superior when it comes to short-range fortitude. With their immense 
-strength and beauty, they are oft likened to war angels leading armies into battle.
-Their strong counterattack as they defend their allies seals the victory.</t>
+          <t>They have no superior when it comes to short-range fortitude. Wielding spears
+and swords, these war angels guard the front line with Circle Protection, shielding
+the entire party from physical assaults while executing swift counterattacks.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1742,18 +1742,18 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Using hand-fans proficiently as weapons, they are skilled in both short and long 
-distance combat. They are unique not only in weapon choice, but also skill selection, 
-most notable of which is an ultimate skill that turns a weakened enemy into... food?</t>
+          <t>Using hand-fans proficiently as weapons, they are skilled in both short and long
+distance combat. Masters of turn delay, they boast unique skills, not least of which
+is an ultimate skill that turns a weakened enemy into... food?</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
